--- a/data/normalo2026.xlsx
+++ b/data/normalo2026.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0C311F-9390-794C-971F-C970383B0A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="16660" yWindow="2000" windowWidth="21180" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Nights" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
+    <sheet name="Nights" sheetId="2" r:id="rId2"/>
+    <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="22">
-  <si>
-    <t>Lights</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="27">
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>mm</t>
   </si>
   <si>
     <t>Chris</t>
@@ -56,44 +57,53 @@
     <t>Noel</t>
   </si>
   <si>
+    <t>Adrianna</t>
+  </si>
+  <si>
+    <t>Alicia</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
-    <t>Adrianna</t>
-  </si>
-  <si>
     <t>Elena</t>
   </si>
   <si>
+    <t>Ella</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>Marla</t>
+  </si>
+  <si>
+    <t>Michelle</t>
+  </si>
+  <si>
     <t>Tiziana</t>
   </si>
   <si>
-    <t>Marla</t>
-  </si>
-  <si>
     <t>Tonia</t>
   </si>
   <si>
-    <t>Michelle</t>
-  </si>
-  <si>
-    <t>Laura</t>
-  </si>
-  <si>
-    <t>Ella</t>
-  </si>
-  <si>
-    <t>Linda</t>
-  </si>
-  <si>
-    <t>Alicia</t>
+    <t>lights</t>
+  </si>
+  <si>
+    <t>episode</t>
+  </si>
+  <si>
+    <t>result</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,17 +114,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -123,18 +129,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FFC5C6C7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -142,47 +142,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -470,300 +444,531 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="10.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8">
-        <v>5</v>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B11DEB-4A4C-C747-BAAE-DAFEAF7FBB70}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="11" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="4" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/normalo2026.xlsx
+++ b/data/normalo2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC404B9D-93AB-9947-A6FD-581B93CD1D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05C07E1-4AAF-E246-9569-DA90FD2006C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9740" yWindow="3560" windowWidth="32520" windowHeight="18420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5880" yWindow="3560" windowWidth="32520" windowHeight="18420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>

--- a/data/normalo2026.xlsx
+++ b/data/normalo2026.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05C07E1-4AAF-E246-9569-DA90FD2006C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="5880" yWindow="3560" windowWidth="32520" windowHeight="18420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
-    <sheet name="Nights" sheetId="2" r:id="rId2"/>
-    <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
-    <sheet name="Solution" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Candidates" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Nights" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Matchboxes" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Solution" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="32">
   <si>
     <t>left</t>
   </si>
@@ -103,28 +94,51 @@
     <t>episode</t>
   </si>
   <si>
+    <t>Mann</t>
+  </si>
+  <si>
+    <t>Frau</t>
+  </si>
+  <si>
     <t>result</t>
+  </si>
+  <si>
+    <t>before_night</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Times"/>
     </font>
   </fonts>
   <fills count="3">
@@ -137,7 +151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5C6C7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,17 +166,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -176,9 +195,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -216,7 +235,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -288,7 +307,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -320,20 +339,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -455,20 +470,60 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="10.6640625" customWidth="1"/>
+    <col min="1" max="3" width="10.714285714285714" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,7 +534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -490,7 +545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -498,7 +553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -506,7 +561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -514,7 +569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -522,7 +577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -530,7 +585,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -538,7 +593,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -546,7 +601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -554,7 +609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -562,25 +617,27 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="1" max="11" width="10.714285714285714" customWidth="1"/>
+    <col min="12" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -615,7 +672,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -650,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -685,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -720,7 +777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -755,7 +812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -790,7 +847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -825,7 +882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -860,7 +917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -895,7 +952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -930,7 +987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -967,32 +1024,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="4" width="10.714285714285714" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1002,11 +1064,14 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1016,11 +1081,14 @@
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1030,11 +1098,14 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1044,11 +1115,14 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1058,11 +1132,14 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1072,11 +1149,14 @@
       <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1086,11 +1166,14 @@
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -1100,21 +1183,34 @@
       <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +1218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1130,7 +1226,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1138,7 +1234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1146,7 +1242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1154,7 +1250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1162,7 +1258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1170,7 +1266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1178,7 +1274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1186,7 +1282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1194,7 +1290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1202,7 +1298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1211,6 +1307,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>